--- a/error_models/conv_models/nv_8x8_b1_dat-1048576_wt-65536_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x8_b1_dat-1048576_wt-65536_int16/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,16 +682,16 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9963588894053546</v>
+        <v>0.997325977787172</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0036339558015872</v>
+        <v>0.0026682645089448</v>
       </c>
       <c r="I2" t="n">
-        <v>7.113336787091126e-06</v>
+        <v>5.716247612287603e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.80011177033516</v>
+        <v>0.8001117703351599</v>
       </c>
       <c r="K2" t="n">
         <v>0.0242914479713724</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>1.213354270529698e-08</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0591719172879862</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.940828082712014</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -616,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.99732369448165</v>
+        <v>0.9974363987394368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0026693383150213</v>
+        <v>0.0025579272394611</v>
       </c>
       <c r="I3" t="n">
-        <v>6.925747057573393e-06</v>
+        <v>5.632564831174562e-06</v>
       </c>
       <c r="J3" t="n">
         <v>0.2619981636229856</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>2.263483406335237e-05</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0591718730851989</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.940828126914801</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -680,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9990387712909786</v>
+        <v>0.999084407408364</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009533069231258999</v>
+        <v>0.0009087531103618</v>
       </c>
       <c r="I4" t="n">
-        <v>7.880329624442981e-06</v>
+        <v>6.798025003075987e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.1407574633591425</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6859365049366798</v>
+        <v>0.6859365049366799</v>
       </c>
       <c r="L4" t="n">
         <v>0.0474833233598351</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>1.717221552336238e-07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0591812050424179</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.940818794957582</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.8896970615347705</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1103029384652296</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9979801502465721</v>
+        <v>0.9980389457709448</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0020119795525832</v>
+        <v>0.0019542838067068</v>
       </c>
       <c r="I5" t="n">
-        <v>7.828744573671975e-06</v>
+        <v>6.728966077369621e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.083219753310193</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7342558565217532</v>
+        <v>0.7342558565217533</v>
       </c>
       <c r="L5" t="n">
         <v>0.07850338801794</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.000489475491033</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0591718651435174</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.9408281348564824</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.9988778732313844</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.0011221267686156</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -808,13 +1250,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9987054390331244</v>
+        <v>0.9987294511176626</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0012867590699948</v>
+        <v>0.0012638412190911</v>
       </c>
       <c r="I6" t="n">
-        <v>7.760440609765289e-06</v>
+        <v>6.666206975283561e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.0500816817821408</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0003164295329572</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0591743555271242</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.9408256444728758</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.9988828038601056</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.0011171961398942</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9961172234178688</v>
+        <v>0.9974293532843032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0038749517493478</v>
+        <v>0.0025641167245114</v>
       </c>
       <c r="I7" t="n">
-        <v>7.783376512422839e-06</v>
+        <v>6.488534914389524e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.7993555141202571</v>
@@ -893,7 +1413,7 @@
         <v>0.0006111443585651</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08088000297919171</v>
+        <v>0.0808800029791918</v>
       </c>
       <c r="O7" t="n">
         <v>0.0283063274023688</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>7.073202308116698e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0591719997139417</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.9408280002860584</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -936,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9967801943473396</v>
+        <v>0.9972366142269954</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0032121756216463</v>
+        <v>0.0027570180073305</v>
       </c>
       <c r="I8" t="n">
-        <v>7.588574743376399e-06</v>
+        <v>6.326309403168429e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6219901218141791</v>
+        <v>0.621990121814179</v>
       </c>
       <c r="K8" t="n">
         <v>0.2015048301813286</v>
@@ -957,7 +1555,7 @@
         <v>0.0076948541477197</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0386432675243165</v>
+        <v>0.0386432675243166</v>
       </c>
       <c r="O8" t="n">
         <v>0.0082802921815374</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0029681732751386</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0591721022437888</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.9408278977562112</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9974995678912112</v>
+        <v>0.9986117979690854</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002492014406554</v>
+        <v>0.0013807224575446</v>
       </c>
       <c r="I9" t="n">
-        <v>8.376245963682797e-06</v>
+        <v>7.438117099088236e-06</v>
       </c>
       <c r="J9" t="n">
         <v>0.6953713380719252</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>4.090607539368672e-07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1064,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9995882247058292</v>
+        <v>0.9996394093671516</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0004037448239383</v>
+        <v>0.0003533750950383</v>
       </c>
       <c r="I10" t="n">
-        <v>7.989013961439541e-06</v>
+        <v>7.174081539179183e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0365255031302754</v>
@@ -1104,6 +1858,84 @@
       </c>
       <c r="T10" t="n">
         <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9997837847299303</v>
+        <v>0.9998428417033348</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002081044267461</v>
+        <v>0.0001500140671908</v>
       </c>
       <c r="I11" t="n">
-        <v>8.069387052720793e-06</v>
+        <v>7.102773203446513e-06</v>
       </c>
       <c r="J11" t="n">
         <v>0.0353869121963865</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9002456533145808</v>
+        <v>0.9002456533145806</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1168,6 +2000,84 @@
       </c>
       <c r="T11" t="n">
         <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9987937388316526</v>
+        <v>0.9990981815657238</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001197675039388</v>
+        <v>0.000894070225622</v>
       </c>
       <c r="I12" t="n">
-        <v>8.544672688485562e-06</v>
+        <v>7.70675238312826e-06</v>
       </c>
       <c r="J12" t="n">
         <v>0.3382410573385364</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>1.072954338521156e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1256,16 +2244,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9991670469146514</v>
+        <v>0.9995505425315488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008245093128039</v>
+        <v>0.000442034897636</v>
       </c>
       <c r="I13" t="n">
-        <v>8.402316273861874e-06</v>
+        <v>7.381114544303113e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3322309369943</v>
+        <v>0.3322309369943001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1283,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5133775793558366</v>
+        <v>0.5133775793558368</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1464555100589102</v>
+        <v>0.1464555100589101</v>
       </c>
       <c r="R13" t="n">
         <v>2.512560921755148e-06</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>3.015015839168943e-07</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9982322242975068</v>
+        <v>0.9986084841623266</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0017593727498018</v>
+        <v>0.0013839255669919</v>
       </c>
       <c r="I14" t="n">
-        <v>8.361496420352315e-06</v>
+        <v>7.548814410372353e-06</v>
       </c>
       <c r="J14" t="n">
         <v>0.4184183372390819</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>0.0003514831705361</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9989918629814588</v>
+        <v>0.9994794997173708</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0009995787281786</v>
+        <v>0.0005129825930411</v>
       </c>
       <c r="I15" t="n">
-        <v>8.516834091523503e-06</v>
+        <v>7.476233316992765e-06</v>
       </c>
       <c r="J15" t="n">
         <v>0.517787993869657</v>
@@ -1405,13 +2549,13 @@
         <v>0.0019818739198723</v>
       </c>
       <c r="N15" t="n">
-        <v>3.268007585883535e-06</v>
+        <v>3.268007585883534e-06</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3186676204528448</v>
+        <v>0.3186676204528447</v>
       </c>
       <c r="Q15" t="n">
         <v>0.1556073136489822</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>1.949599029963217e-07</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9997891094207968</v>
+        <v>0.9998600576336282</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002029050292598</v>
+        <v>0.0001330448664664</v>
       </c>
       <c r="I16" t="n">
-        <v>7.94409367269348e-06</v>
+        <v>6.856043634542106e-06</v>
       </c>
       <c r="J16" t="n">
         <v>0.0468165773372553</v>
@@ -1469,7 +2691,7 @@
         <v>0.0016804629243546</v>
       </c>
       <c r="N16" t="n">
-        <v>6.367295605903689e-06</v>
+        <v>6.367295605903688e-06</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>5.674585620097137e-07</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9990774192633496</v>
+        <v>0.9992066744309552</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0009142890906676</v>
+        <v>0.0007858577866078</v>
       </c>
       <c r="I17" t="n">
-        <v>8.250189711983574e-06</v>
+        <v>7.426326165789833e-06</v>
       </c>
       <c r="J17" t="n">
         <v>0.1356676130015488</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.001063298872992</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9997620414776268</v>
+        <v>0.9998873362392818</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0002298133311672</v>
+        <v>0.0001056035568481</v>
       </c>
       <c r="I18" t="n">
-        <v>8.103734935144233e-06</v>
+        <v>7.01874759904718e-06</v>
       </c>
       <c r="J18" t="n">
         <v>0.117455119460382</v>
@@ -1597,7 +2975,7 @@
         <v>0.0016397350880894</v>
       </c>
       <c r="N18" t="n">
-        <v>6.076652060756106e-06</v>
+        <v>6.076652060756105e-06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>0.0005438909864936</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1640,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9996472048956954</v>
+        <v>0.999672963439318</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0003448021350194</v>
+        <v>0.0003199183756825</v>
       </c>
       <c r="I19" t="n">
-        <v>7.951513014306944e-06</v>
+        <v>7.076728728499288e-06</v>
       </c>
       <c r="J19" t="n">
         <v>0.0015042475977246</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8697561256496408</v>
+        <v>0.8697561256496409</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1680,6 +3136,84 @@
       </c>
       <c r="T19" t="n">
         <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1704,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.999847945374018</v>
+        <v>0.999904694637156</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0001441743481829</v>
+        <v>8.847279451585773e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>7.838821528012026e-06</v>
+        <v>6.791112057079803e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0352339974580091</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9446273959987086</v>
+        <v>0.9446273959987084</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1744,6 +3278,84 @@
       </c>
       <c r="T20" t="n">
         <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1768,19 +3380,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9996232832301644</v>
+        <v>0.9996403668935336</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0003686604697634</v>
+        <v>0.0003523968608986</v>
       </c>
       <c r="I21" t="n">
-        <v>8.0148438012003e-06</v>
+        <v>7.19478929663787e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0196658694636547</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8831385983380496</v>
+        <v>0.8831385983380495</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1808,6 +3420,84 @@
       </c>
       <c r="T21" t="n">
         <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1832,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0950921425911002</v>
+        <v>0.6193272051626191</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9048999065401652</v>
+        <v>0.3806655903844561</v>
       </c>
       <c r="I22" t="n">
-        <v>7.90941246345844e-06</v>
+        <v>7.162996653763435e-06</v>
       </c>
       <c r="J22" t="n">
         <v>0.0005680251283367</v>
@@ -1872,6 +3562,84 @@
       </c>
       <c r="T22" t="n">
         <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0975281618918829</v>
+        <v>0.6213077960379293</v>
       </c>
       <c r="H23" t="n">
-        <v>0.902463208688618</v>
+        <v>0.3786843041789427</v>
       </c>
       <c r="I23" t="n">
-        <v>8.587963228004021e-06</v>
+        <v>7.858326857076171e-06</v>
       </c>
       <c r="J23" t="n">
         <v>2.129958341752911e-06</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1960,16 +3806,16 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.997582057333622</v>
+        <v>0.9979284813395261</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0024097425235353</v>
+        <v>0.0020641154228414</v>
       </c>
       <c r="I24" t="n">
-        <v>8.158686571771699e-06</v>
+        <v>7.361781361487744e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2968476130113125</v>
+        <v>0.2968476130113124</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1981,13 +3827,13 @@
         <v>0.008009153001427899</v>
       </c>
       <c r="N24" t="n">
-        <v>2.60086726645094e-06</v>
+        <v>2.600867266450941e-06</v>
       </c>
       <c r="O24" t="n">
         <v>1.02614531954846e-10</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5187206398157964</v>
+        <v>0.5187206398157965</v>
       </c>
       <c r="Q24" t="n">
         <v>0.1739054122581353</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>9.401281109427855e-05</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9987218429528152</v>
+        <v>0.9987784034381952</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0012699550987407</v>
+        <v>0.0012141800784011</v>
       </c>
       <c r="I25" t="n">
-        <v>8.160492172929935e-06</v>
+        <v>7.375027132629109e-06</v>
       </c>
       <c r="J25" t="n">
         <v>0.057883978182045</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0008462531158285</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9990405905865128</v>
+        <v>0.9990857281320432</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0009515297099151</v>
+        <v>0.0009074556493662</v>
       </c>
       <c r="I26" t="n">
-        <v>7.83824730123725e-06</v>
+        <v>6.774762319528112e-06</v>
       </c>
       <c r="J26" t="n">
         <v>0.0360933211751679</v>
@@ -2115,7 +4117,7 @@
         <v>0.0271693047146126</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7803726564987307</v>
+        <v>0.7803726564987308</v>
       </c>
       <c r="Q26" t="n">
         <v>4.622921315342578e-06</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0122831131454036</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.0591723419849495</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.9408276580150504</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.059172284602423</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.9408277153975768</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2152,19 +4232,19 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9967125336728972</v>
+        <v>0.997000667592176</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0032798025079218</v>
+        <v>0.0029929249535063</v>
       </c>
       <c r="I27" t="n">
-        <v>7.622362910170992e-06</v>
+        <v>6.365998046606683e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.4729451774276768</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3493486304978426</v>
+        <v>0.3493486304978427</v>
       </c>
       <c r="L27" t="n">
         <v>0.1102307796079593</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0063221335524419</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.0591721919574049</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.9408278080425948</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.0588208698036495</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.9411791301963504</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2216,16 +4374,16 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9979711717217156</v>
+        <v>0.9981265203332008</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0020210822700457</v>
+        <v>0.0018669124292443</v>
       </c>
       <c r="I28" t="n">
-        <v>7.70455196771472e-06</v>
+        <v>6.525781283642411e-06</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1998104425746424</v>
+        <v>0.1998104425746423</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2243,7 +4401,7 @@
         <v>0.024150523894468</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6181228238705528</v>
+        <v>0.618122823870553</v>
       </c>
       <c r="Q28" t="n">
         <v>2.309593501083851e-05</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0026460271586042</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.0591746127600397</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.9408253872399605</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9968228950982704</v>
+        <v>0.9969480286969794</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0031694027959264</v>
+        <v>0.0030454250360257</v>
       </c>
       <c r="I29" t="n">
-        <v>7.660649532204819e-06</v>
+        <v>6.504810723927915e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.2588131821993297</v>
@@ -2307,10 +4543,10 @@
         <v>0.0298586314820326</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5586891179803275</v>
+        <v>0.5586891179803277</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.60692081512283e-06</v>
+        <v>5.606920815122831e-06</v>
       </c>
       <c r="R29" t="n">
         <v>0.0004269007227619</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0059339828185068</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.0004013357521518</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.9995986642478482</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.9988914929339512</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.0011085070660489</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2344,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.093057684437255</v>
+        <v>0.6175744084725504</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9069341199816688</v>
+        <v>0.3824181275785654</v>
       </c>
       <c r="I30" t="n">
-        <v>8.154124805355226e-06</v>
+        <v>7.422492613197082e-06</v>
       </c>
       <c r="J30" t="n">
         <v>0.0001913313568092</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9967739152149824</v>
+        <v>0.9967739152149822</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2384,6 +4698,84 @@
       </c>
       <c r="T30" t="n">
         <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2408,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9944792265939444</v>
+        <v>0.9950360604694526</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0055127190003882</v>
+        <v>0.0049566776392767</v>
       </c>
       <c r="I31" t="n">
-        <v>8.012949396311159e-06</v>
+        <v>7.220434999696359e-06</v>
       </c>
       <c r="J31" t="n">
         <v>0.059198138610777</v>
       </c>
       <c r="K31" t="n">
-        <v>0.771349973216191</v>
+        <v>0.7713499732161909</v>
       </c>
       <c r="L31" t="n">
         <v>5.062690053525888e-08</v>
@@ -2435,7 +4827,7 @@
         <v>6.234084798871832e-07</v>
       </c>
       <c r="P31" t="n">
-        <v>1.525191678870807e-06</v>
+        <v>1.525191678870808e-06</v>
       </c>
       <c r="Q31" t="n">
         <v>0.1615213417949524</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>7.906444777336139e-07</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0985719277129334</v>
+        <v>0.6226548118500984</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9014191401828427</v>
+        <v>0.3773370108992697</v>
       </c>
       <c r="I32" t="n">
-        <v>8.890647952744593e-06</v>
+        <v>8.13579436099099e-06</v>
       </c>
       <c r="J32" t="n">
         <v>2.255394776322286e-06</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>7.27546702039402e-08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0984854930687462</v>
+        <v>0.4321143451111657</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9015075656824824</v>
+        <v>0.5678800271261893</v>
       </c>
       <c r="I33" t="n">
-        <v>6.899792500396236e-06</v>
+        <v>5.586306373886888e-06</v>
       </c>
       <c r="J33" t="n">
         <v>1.394660437529913e-05</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1952747247351675</v>
+        <v>0.4883191024431103</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8047184092722645</v>
+        <v>0.5116753943997867</v>
       </c>
       <c r="I34" t="n">
-        <v>6.824536296897877e-06</v>
+        <v>5.461700831974303e-06</v>
       </c>
       <c r="J34" t="n">
         <v>2.414692157164051e-06</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>1.698515392344097e-07</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9944429755491366</v>
+        <v>0.9967311456387563</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00554943512154025</v>
+        <v>0.00326258315559235</v>
       </c>
       <c r="I35" t="n">
-        <v>7.547873052055149e-06</v>
+        <v>6.229749380490808e-06</v>
       </c>
       <c r="J35" t="n">
         <v>0.8183895106773195</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>0.003220688821493417</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.05917203931888435</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.9408279606811156</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2728,16 +5510,16 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4620064207329094</v>
+        <v>0.6465794711940647</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5379865457190175</v>
+        <v>0.3534147461766293</v>
       </c>
       <c r="I36" t="n">
-        <v>6.99209180200669e-06</v>
+        <v>5.741173035032073e-06</v>
       </c>
       <c r="J36" t="n">
-        <v>0.356813363060472</v>
+        <v>0.3568133630604721</v>
       </c>
       <c r="K36" t="n">
         <v>0.6419466889238448</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>1.000592000625254e-05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.00020050779876615</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.9997994922012339</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2792,16 +5652,16 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9930867006707812</v>
+        <v>0.9935977712700801</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0069056956639202</v>
+        <v>0.006395884717521</v>
       </c>
       <c r="I37" t="n">
-        <v>7.562209027726541e-06</v>
+        <v>6.302556128018065e-06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6285325958687593</v>
+        <v>0.6285325958687592</v>
       </c>
       <c r="K37" t="n">
         <v>0.1909763365367488</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.00333305886194425</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9959293734972855</v>
+        <v>0.9960359395740538</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00406280831396295</v>
+        <v>0.00395742816450615</v>
       </c>
       <c r="I38" t="n">
-        <v>7.776732480606366e-06</v>
+        <v>6.590805169095716e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.1942184271673125</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.00339498050069685</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.9705882352941175</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.5290263993456593</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.4709736006543406</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,19 +5936,19 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9976793368023505</v>
+        <v>0.9977322409585381</v>
       </c>
       <c r="H39" t="n">
-        <v>0.002312849652464525</v>
+        <v>0.00226095703049095</v>
       </c>
       <c r="I39" t="n">
-        <v>7.772088913907803e-06</v>
+        <v>6.760554699829769e-06</v>
       </c>
       <c r="J39" t="n">
         <v>0.04918414855254639</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2580755821491343</v>
+        <v>0.2580755821491344</v>
       </c>
       <c r="L39" t="n">
         <v>0.0194695932351663</v>
@@ -2947,7 +5963,7 @@
         <v>0.02400327659592968</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5676281492873124</v>
+        <v>0.5676281492873125</v>
       </c>
       <c r="Q39" t="n">
         <v>6.164402024479878e-06</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.0022768571771186</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.04437930367958817</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.7056206963204118</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.7490655786250717</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.000934421374928225</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2984,19 +6078,19 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9990515291049011</v>
+        <v>0.9990676845336829</v>
       </c>
       <c r="H40" t="n">
-        <v>0.000940754597395</v>
+        <v>0.0009255791008759501</v>
       </c>
       <c r="I40" t="n">
-        <v>7.674841432927303e-06</v>
+        <v>6.694909170185604e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.005699690649424501</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4881259821198352</v>
+        <v>0.488125982119835</v>
       </c>
       <c r="L40" t="n">
         <v>0.0120106918434804</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.00126462613145325</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.0295873173020293</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.4704126826979706</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.4990679191936006</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.0009320808063993</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_8x8_b1_dat-1048576_wt-65536_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x8_b1_dat-1048576_wt-65536_int16/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,321 +425,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.997325977787172</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0026682645089448</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>5.716247612287603e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.8001117703351599</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0242914479713724</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0604821704976181</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0016747277757463</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0604839086633186</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0378005031064983</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1.619531728794083e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>3.223812761351302e-05</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>3.968892907758498e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>1.060933395742089e-06</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>1.213354270529698e-08</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
         <v>1</v>
@@ -754,25 +759,25 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.0591719172879862</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
         <v>0.940828082712014</v>
       </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -781,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -793,95 +798,101 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9974363987394368</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0025579272394611</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>5.632564831174562e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.2619981636229856</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.5650508781015436</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.1413026237334559</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0070797883342723</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0135871322755148</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0108676311299508</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>2.724792351675668e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>2.483116347310066e-05</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>2.425783915531061e-05</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>3.92629996215344e-05</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>2.263483406335237e-05</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>1</v>
@@ -896,25 +907,25 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.0591718730851989</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.940828126914801</v>
       </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -923,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -932,98 +943,104 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.999084407408364</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0009087531103618</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>6.798025003075987e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.1407574633591425</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.6859365049366799</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0474833233598351</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0038249122909702</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.1053889383393881</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0158077047638933</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.016221346354662e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>2.173340416630487e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0007178547993922</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>6.030529431747818e-05</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1.717221552336238e-07</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>1</v>
@@ -1038,25 +1055,25 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.0591812050424179</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.940818794957582</v>
       </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1065,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1074,98 +1091,104 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0.8896970615347705</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>0.1103029384652296</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9980389457709448</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0019542838067068</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>6.728966077369621e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.083219753310193</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.7342558565217533</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.07850338801794</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.008898219967585601</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0685797482800127</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0220416576925038</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>4.836932186662566e-07</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0024538759880328</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0012016646007627</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0003557744513851</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.000489475491033</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>1</v>
@@ -1180,25 +1203,25 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.0591718651435174</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.9408281348564824</v>
       </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1207,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1216,98 +1239,104 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.9988778732313844</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>0.0011221267686156</v>
       </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9987294511176626</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0012638412190911</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>6.666206975283561e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.0500816817821408</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.7686214773188683</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.06731377827551389</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0055039495821395</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.09089995501096861</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0158077228955672</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>4.675314318975175e-07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>4.942450038625608e-06</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0013967284290168</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>5.280186309436903e-05</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0003164295329572</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
         <v>1</v>
@@ -1322,25 +1351,25 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.0591743555271242</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.9408256444728758</v>
       </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1349,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1358,98 +1387,104 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0.9988828038601056</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>0.0011171961398942</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9974293532843032</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0025641167245114</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>6.488534914389524e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.7993555141202571</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0301549665124952</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.0404418863595993</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.0006111443585651</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0808800029791918</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0283063274023688</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1.906659439892104e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0202467883094742</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1.050266935155606e-07</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>6.094954130626989e-07</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>7.073202308116698e-07</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>1</v>
@@ -1464,25 +1499,25 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.0591719997139417</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.9408280002860584</v>
       </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1491,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1509,89 +1544,95 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9972366142269954</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0027570180073305</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>6.326309403168429e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.621990121814179</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.2015048301813286</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.1076433295972528</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0076948541477197</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0386432675243166</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0082802921815374</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>2.669809137993021e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.008302115096197099</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.0001046088966088</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.0001056354847664</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0029681732751386</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1606,25 +1647,25 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.0591721022437888</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.9408278977562112</v>
       </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1633,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -1651,89 +1692,95 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9986117979690854</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0013807224575446</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>7.438117099088236e-06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.6953713380719252</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.1354040715900206</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0019884359403448</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>4.263659250538324e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>3.458130545530564e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.1672230547484069</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.167123804537187e-06</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>3.760218676696748e-06</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>4.090607539368672e-07</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
         <v>1</v>
@@ -1748,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1757,16 +1804,16 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1775,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -1787,78 +1834,84 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9996394093671516</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0003533750950383</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>7.174081539179183e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0365255031302754</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.8517604589090847</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0017698146267431</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>5.360588757610534e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>5.749467990816146e-08</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.1086963222110588</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0012424415831293</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
@@ -1869,16 +1922,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1890,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1902,13 +1955,13 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -1923,84 +1976,90 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9998428417033348</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0001500140671908</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>7.102773203446513e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0353869121963865</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.9002456533145806</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.0005451370278628</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>5.003197565695717e-06</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>2.001302967972618e-08</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0632686988392667</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0005485339550368</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
@@ -2011,16 +2070,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2032,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2044,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2065,101 +2124,107 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9990981815657238</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.000894070225622</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7.70675238312826e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.3382410573385364</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.263537343577252e-08</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.005448498627316</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>2.945504490266549e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.4866085977085421</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.1642533081728887</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>2.408761402355785e-06</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0054420368408412</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1.072954338521156e-06</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -2174,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2186,13 +2251,13 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2201,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2213,95 +2278,101 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9995505425315488</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.000442034897636</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>7.381114544303113e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.3322309369943001</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.246473296842111e-08</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.0009939163102894999</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>3.825087781132482e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.5133775793558368</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1464555100589101</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>2.512560921755148e-06</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0069353442093726</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>3.015015839168943e-07</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
         <v>1</v>
@@ -2316,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2328,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2343,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -2355,95 +2426,101 @@
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9986084841623266</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0013839255669919</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>7.548814410372353e-06</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.4184183372390819</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>5.241190096411788e-08</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.0050986599024689</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>2.522520187932498e-06</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.4134015757998396</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.1578098740105418</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0.0001774067956639</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0047400466935075</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.0003514831705361</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
@@ -2458,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2470,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2485,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -2494,98 +2571,104 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9994794997173708</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0005129825930411</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>7.476233316992765e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.517787993869657</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0019818739198723</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>3.268007585883534e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.3186676204528447</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1556073136489822</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>3.233921769353074e-06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0059484597631143</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>1.949599029963217e-07</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -2600,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2612,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2627,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -2639,95 +2722,101 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9998600576336282</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.0001330448664664</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>6.856043634542106e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.0468165773372553</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.000840448899132</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>4.766570068248497e-08</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0016804629243546</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>6.367295605903688e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.8648846633287173</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0790636326804675</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>4.815395170029211e-06</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0067023755587636</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>5.674585620097137e-07</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>1</v>
@@ -2742,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2754,13 +2843,13 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -2769,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -2781,95 +2870,101 @@
         <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9992066744309552</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0007858577866078</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>7.426326165789833e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.1356676130015488</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0010623933558163</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.000530220656783</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.0050491118968958</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>5.686111740714032e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>1.336634853189426e-08</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.6868691803274966</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.166962616363011</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0006663903528102</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0021234342382858</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.001063298872992</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
@@ -2884,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2902,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -2911,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -2920,98 +3015,104 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998873362392818</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0001056035568481</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>7.01874759904718e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.117455119460382</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>3.931293930496648e-06</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>6.536884527854345e-08</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.0016397350880894</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>6.076652060756105e-06</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.8379221467776402</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.0348031481591954</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>4.593206519227676e-06</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0076212515505726</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.0005438909864936</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
         <v>1</v>
@@ -3026,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3038,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3053,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -3065,78 +3166,84 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.999672963439318</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0003199183756825</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>7.076728728499288e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0015042475977246</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.8697561256496409</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0013017782123945</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>5.314965568186122e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>3.896193371416371e-09</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.1264817613053745</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0009507269168328</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -3147,16 +3254,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3168,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3180,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3201,84 +3308,90 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.999904694637156</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>8.847279451585773e-05</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>6.791112057079803e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0352339974580091</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.9446273959987084</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>2.03190285524235e-06</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>5.370301061448489e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>1.294297425042335e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0193499677325032</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.000781182207617</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -3289,16 +3402,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3310,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3322,13 +3435,13 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3343,84 +3456,90 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9996403668935336</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0003523968608986</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>7.19478929663787e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0196658694636547</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.8831385983380495</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0011129210300855</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>5.091923822877716e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>8.038459509201347e-08</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.0948511155498899</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0012262818536312</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -3431,16 +3550,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3452,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3464,13 +3583,13 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3485,81 +3604,87 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6193272051626191</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3806655903844561</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>7.162996653763435e-06</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0005680251283367</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9960328857804422</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>7.455011807378073e-08</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2.514172166928244e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>3.8115300155402e-09</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0033989441315803</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -3573,13 +3698,13 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3627,87 +3752,93 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.6213077960379293</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.3786843041789427</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>7.858326857076171e-06</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>2.129958341752911e-06</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9986545671369136</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.468936787415746e-07</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>2.985306323443793e-08</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.91227673330922e-09</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0013430820708196</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>7.18635248706641e-10</v>
       </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
@@ -3715,22 +3846,22 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3769,101 +3900,107 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9979284813395261</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0020641154228414</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>7.361781361487744e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.2968476130113124</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.4413427461499e-08</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.008009153001427899</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2.600867266450941e-06</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>1.02614531954846e-10</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.5187206398157965</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1739054122581353</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>2.189459839615361e-06</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0024183028028144</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>9.401281109427855e-05</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
         <v>1</v>
@@ -3878,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3890,13 +4027,13 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -3905,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -3917,95 +4054,101 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9987784034381952</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0012141800784011</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>7.375027132629109e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.057883978182045</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0011927872428622</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>4.974777307227113e-05</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0071119952854791</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>3.804206927749537e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>8.459178317283835e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.7684096713817242</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1632549384790599</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0007498838397162</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0004968905778352999</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0008462531158285</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
         <v>1</v>
@@ -4020,13 +4163,13 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -4038,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4047,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -4056,98 +4199,104 @@
         <v>1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9990857281320432</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0009074556493662</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>6.774762319528112e-06</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0360933211751679</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0176722231032708</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0387005446258437</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0045540813899094</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0760802026895837</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0271693047146126</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.7803726564987308</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>4.622921315342578e-06</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0063180999665768</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0007517830904767</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0122831131454036</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4162,25 +4311,25 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.0591723419849495</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>0.9408276580150504</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4189,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -4198,98 +4347,104 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.059172284602423</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>0.9408277153975768</v>
       </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.997000667592176</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0029929249535063</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>6.365998046606683e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.4729451774276768</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.3493486304978427</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1102307796079593</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0082803142000202</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0279481371386712</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0124202684553457</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>2.506824869526108e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0062324927928004</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.0016092888210464</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>2.680522058296872e-06</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0063221335524419</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -4304,25 +4459,25 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.0591721919574049</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>0.9408278080425948</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4331,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -4340,98 +4495,104 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.0588208698036495</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>0.9411791301963504</v>
       </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9981265203332008</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0018669124292443</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>6.525781283642411e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.1998104425746423</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.0748673218731266</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0052085216304784</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0652096996186378</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.024150523894468</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.618122823870553</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>2.309593501083851e-05</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>7.887988593460414e-07</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.005130652308444</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0026460271586042</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
@@ -4446,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4455,16 +4616,16 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4473,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -4482,98 +4643,104 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
         <v>0.0591746127600397</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AT28" t="n">
         <v>0.9408253872399605</v>
       </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9969480286969794</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0030454250360257</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>6.504810723927915e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.2588131821993297</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0860636471398029</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0119438318335171</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0474269317063804</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0298586314820326</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.5586891179803277</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>5.606920815122831e-06</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0004269007227619</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0008381004058669</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0059339828185068</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
         <v>1</v>
@@ -4588,25 +4755,25 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
         <v>0.0004013357521518</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>0.9995986642478482</v>
       </c>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -4615,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -4624,81 +4791,87 @@
         <v>1</v>
       </c>
       <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
         <v>0.9988914929339512</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AT29" t="n">
         <v>0.0011085070660489</v>
       </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.6175744084725504</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3824181275785654</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>7.422492613197082e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0001913313568092</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9967739152149822</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>7.48318830768589e-08</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>2.94468253254166e-08</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>3.828914416979365e-09</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0030345293941004</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>7.447021441025244e-08</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
@@ -4709,22 +4882,22 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4763,101 +4936,107 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9950360604694526</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0049566776392767</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>7.220434999696359e-06</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.059198138610777</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.7713499732161909</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>5.062690053525888e-08</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.0079207335044791</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>5.984355587732915e-06</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>6.234084798871832e-07</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>1.525191678870808e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.1615213417949524</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>7.917354322312394e-07</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>5.454772488127061e-09</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>7.906444777336139e-07</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
@@ -4866,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4881,16 +5060,16 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -4899,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -4911,104 +5090,110 @@
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.6226548118500984</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.3773370108992697</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>8.13579436099099e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>2.255394776322286e-06</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.9994176136981668</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>7.357956297562269e-07</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>4.694466783938093e-07</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>9.453710427058014e-09</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.0005785837360865</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.182640106118345e-07</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>7.27546702039402e-08</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5047,87 +5232,93 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.4321143451111657</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.5678800271261893</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>5.586306373886888e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>1.394660437529913e-05</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.9999372575574748</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>4.820561531703417e-05</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>1.394396493950454e-07</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>1.297149822393924e-08</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>3.699346609991379e-08</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>2.848118302127966e-07</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
         <v>7.455011807378073e-08</v>
       </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
@@ -5135,22 +5326,22 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5165,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5183,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -5195,104 +5386,110 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.4883191024431103</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.5116753943997867</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>5.461700831974303e-06</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>2.414692157164051e-06</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.9990716259949504</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>8.009483903093517e-05</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>2.822298629341983e-07</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0006331856571467</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2.891150635873695e-08</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>1.13670381924914e-06</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
       <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.698515392344097e-07</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5307,13 +5504,13 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -5325,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -5337,95 +5534,101 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9967311456387563</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.00326258315559235</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>6.229749380490808e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.8183895106773195</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.010336508520846</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.0547446383175571</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.0005807108915952802</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.0579653389165441</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.02898031823899505</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.751788782203428e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.0257794485994303</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.961492152920544e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>8.236603620180488e-07</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.003220688821493417</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
@@ -5440,25 +5643,25 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0.05917203931888435</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>0.9408279606811156</v>
       </c>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -5467,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -5485,123 +5688,129 @@
         <v>0</v>
       </c>
       <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.6465794711940647</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.3534147461766293</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>5.741173035032073e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.3568133630604721</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.6419466889238448</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.00069248162735775</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>1.918904154198876e-05</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.0002603876172891</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.0001343220085030842</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>8.456946568737476e-07</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.0001124996246449478</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>2.221659811801357e-07</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>3.120271168967022e-07</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>1.000592000625254e-05</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
       <c r="AF36" t="n">
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
         <v>0.00020050779876615</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.9997994922012339</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AK36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
@@ -5609,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -5627,89 +5836,95 @@
         <v>0</v>
       </c>
       <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9935977712700801</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.006395884717521</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>6.302556128018065e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.6285325958687592</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.1909763365367488</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.1099313299473529</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.009625585504753599</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.03799304224618386</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.0155826575408101</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>2.46002711621014e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.00237129964521615</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.000440032820334953</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>9.990895544868179e-07</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.00333305886194425</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -5724,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5733,16 +5948,16 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -5751,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -5769,89 +5984,95 @@
         <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9960359395740538</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.00395742816450615</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>6.590805169095716e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.1942184271673125</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.0878561361858773</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.009449379195987</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.0581246169868245</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.0151489332389657</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.6259469688493504</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.0008124066780569986</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0008935495565393906</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.00093452288934675</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.00339498050069685</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
         <v>1</v>
@@ -5866,25 +6087,25 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.9705882352941175</v>
       </c>
-      <c r="AI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -5893,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -5902,102 +6123,108 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
         <v>0.5290263993456593</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AT38" t="n">
         <v>0.4709736006543406</v>
       </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9977322409585381</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.00226095703049095</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>6.760554699829769e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.04918414855254639</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2580755821491344</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.0194695932351663</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.005191649128668925</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.07088076151511885</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.02400327659592968</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.5676281492873125</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>6.164402024479878e-06</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.001276363302596425</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>9.640512611391756e-05</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.0022768571771186</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
         <v>0.75</v>
       </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
@@ -6008,25 +6235,25 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0.04437930367958817</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.7056206963204118</v>
       </c>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6035,111 +6262,117 @@
         <v>0</v>
       </c>
       <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
         <v>0.7490655786250717</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>0.000934421374928225</v>
       </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9990676845336829</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0009255791008759501</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>6.694909170185604e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.005699690649424501</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.488125982119835</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0120106918434804</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.00234264057808545</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.05335642016233755</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.0283216423510745</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.4075751012509998</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>1.082249434470945e-05</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00126788369536205</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>2.445513453289041e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.00126462613145325</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
@@ -6150,25 +6383,25 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.0295873173020293</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>0.4704126826979706</v>
       </c>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6177,24 +6410,30 @@
         <v>0</v>
       </c>
       <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
         <v>0.4990679191936006</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>0.0009320808063993</v>
       </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>1</v>
       </c>
     </row>
